--- a/store/Jul-2026/Mail Attachment/Non_BTC_Report_28-Jul-2026.xlsx
+++ b/store/Jul-2026/Mail Attachment/Non_BTC_Report_28-Jul-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,37 +518,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990269</t>
+          <t>WTI-20260728-3990925</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Megha Arora</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IBM India Private Limited</t>
+          <t>Concentrix Daksh Services India Private Limited</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DR. MANI MADHUKAR</t>
+          <t>YOGENDRA JAIN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-28 07:30:00</t>
+          <t>2026-07-28 14:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9560055140</t>
+          <t>9811804462</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>manimad9@in.ibm.com</t>
+          <t>megha.arora1@concentrix.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Priya Rautela</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-27 22:24:43.037000</t>
+          <t>2026-07-28 13:08:05.123000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -573,53 +573,57 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Airport Transfer Rate : 1500.00 ] PkgID:[288380]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990262</t>
+          <t>WTI-20260728-3990869</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Vishnu Dutt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IBM India Private Limited</t>
+          <t>Vishnu C/o Pernod Ricard India Private Limited</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SHANKAR SUBRAMANIAN</t>
+          <t>SHASHANK NIMESH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-28 09:00:00</t>
+          <t>2026-07-28 15:15:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9500063686</t>
+          <t>8397850830</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>shankasu@in.ibm.com</t>
+          <t>shashank.nimesh@pernod-ricard.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -629,12 +633,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-27 22:16:42.720000</t>
+          <t>2026-07-28 12:30:52.990000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -644,7 +648,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Hyderabad Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -660,52 +664,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990639</t>
+          <t>WTI-20260728-3991079</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cargill India Private Limited</t>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIVYA T</t>
+          <t>PALLAVI WALIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-28 10:00:00</t>
+          <t>2026-07-28 16:00:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9361162833</t>
+          <t>9810649593</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Divya_T@cargill.com</t>
+          <t>pallaviwalia@microsoft.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PG link</t>
+          <t>E-Mandate</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-28 09:11:29.883000</t>
+          <t>2026-07-28 14:47:46.040000</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -723,15 +727,27 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990528</t>
+          <t>WTI-20260728-3991046</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -746,22 +762,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTOSH SHETTY</t>
+          <t>DIMPLE ATHA /MAHESH DUBEY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-28 10:15:00</t>
+          <t>2026-07-28 16:30:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9773344129</t>
+          <t>9820198700</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>santosh.k.shetty@citi.com</t>
+          <t>dimple.atha@citi.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -771,12 +787,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-07-28 03:40:09.987000</t>
+          <t>2026-07-28 14:33:09.500000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -791,60 +807,64 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ss22254</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>ss22254</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ss22254</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 2295.00 ] PkgID:[287904]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990625</t>
+          <t>WTI-20260728-3990867</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transport Desk Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coca-Cola India Pvt. Ltd - Direct</t>
+          <t>Google India Private Limited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VENKAT PRASUN</t>
+          <t>SUMANA TALLA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-28 11:00:00</t>
+          <t>2026-07-28 18:00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9701327125</t>
+          <t>6309985478</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>vprasun@coca-cola.com</t>
+          <t>sumanat@google.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -859,7 +879,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-07-28 08:25:47.897000</t>
+          <t>2026-07-28 12:29:04.750000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -869,7 +889,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -897,37 +917,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990358</t>
+          <t>WTI-20260728-3991230</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Megha Arora</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Qualcomm India Private Limited-CRD</t>
+          <t>Concentrix Daksh Services India Private Limited</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NIKITHA SHEKAR</t>
+          <t>YOGENDRA JAIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-28 11:15:00</t>
+          <t>2026-07-28 19:25:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9663826684</t>
+          <t>9811804462</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nikitha@qualcomm.com</t>
+          <t>megha.arora1@concentrix.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -937,38 +957,54 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-07-27 23:37:28.030000</t>
+          <t>2026-07-28 16:09:48.703000</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Chennai Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1150.00 ] PkgID:[288511]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990617</t>
+          <t>WTI-20260728-3990935</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -978,27 +1014,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Citibank  NA</t>
+          <t>Alstom Transport India Limited-CRD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BHUSHAN SHINTRE</t>
+          <t>AMIT TIWARI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-28 12:00:00</t>
+          <t>2026-07-28 21:00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9923445651</t>
+          <t>9106876905</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bhushan.shintre@citi.com</t>
+          <t>amit.tiwari@alstomgroup.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1008,38 +1044,54 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-28 07:54:09.363000</t>
+          <t>2026-07-28 13:13:46.933000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1300.00 ] PkgID:[175442]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990592</t>
+          <t>WTI-20260728-3990938</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1049,27 +1101,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Concentrix Daksh Services India Private Limited</t>
+          <t>IBM India Private Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MADHUSUDAN SHARMA</t>
+          <t>PIYALI HAZRA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-28 13:30:00</t>
+          <t>2026-07-28 22:45:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9899692733</t>
+          <t>7064012261</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>madhusudan.sharma@concentrix.com</t>
+          <t>Piyali.Hazra@ibm.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1079,12 +1131,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-28 05:46:09.200000</t>
+          <t>2026-07-28 13:16:28.223000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1094,7 +1146,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1102,64 +1154,76 @@
           <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Airport Transfer Rate : 1500.00 ] PkgID:[288392]</t>
+          <t>Airport - Transfer Rate : 1500.00 ] PkgID:[212268]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990623</t>
+          <t>WTI-20260728-3991197</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANJIB KUMAR SINHA</t>
+          <t>MAHESH DUBEY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-29 05:30:00</t>
+          <t>2026-07-28 23:30:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9899986149</t>
+          <t>8931038516</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sanjibks@microsoft.com</t>
+          <t>md56125@citi.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-07-28 08:15:39.080000</t>
+          <t>2026-07-28 15:57:17.987000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1169,7 +1233,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1177,49 +1241,61 @@
           <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Airport Transfer Rate : 2500.00 ] PkgID:[258138]</t>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 2295.00 ] PkgID:[287934]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990627</t>
+          <t>WTI-20260728-3990833</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Transport Desk Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coca-Cola India Pvt. Ltd - Direct</t>
+          <t>IBM India Private Limited</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VENKAT PRASUN</t>
+          <t>ABHED KULKARNI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-29 07:00:00</t>
+          <t>2026-07-29 05:00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9701327125</t>
+          <t>9822683464</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>vprasun@coca-cola.com</t>
+          <t>abhed.kulkarni@in.ibm.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1234,7 +1310,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-07-28 08:26:48.280000</t>
+          <t>2026-07-28 11:57:44.777000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1244,7 +1320,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Tirupati</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1254,55 +1330,47 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>053704</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990593</t>
+          <t>WTI-20260728-3991178</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Vishnu Dutt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Concentrix Daksh Services India Private Limited</t>
+          <t>Vishnu C/o Pernod Ricard India Private Limited</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MADHUSUDAN SHARMA</t>
+          <t>ASHOK BAGHEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-29 08:30:00</t>
+          <t>2026-07-29 05:15:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9899692733</t>
+          <t>9810526579</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>madhusudan.sharma@concentrix.com</t>
+          <t>Vishnu.Dutt-ext@pernod-ricard.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1312,27 +1380,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Vikram.Sharma</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-07-28 05:47:49.073000</t>
+          <t>2026-07-28 15:43:47.710000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Outstation</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1343,37 +1411,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990094</t>
+          <t>WTI-20260728-3990790</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nishant Marathe</t>
+          <t>MISHRA Jay</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BP Business Solutions India Private Ltd- SEZ</t>
+          <t>Sopra Steria India Ltd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHANDRA KUMAR MEDA + KULEN MARKANDU</t>
+          <t>DEEPA KAUL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-29 08:30:00</t>
+          <t>2026-07-29 07:00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+44758600150</t>
+          <t>9910041451</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>chandra.kumar@bp.com</t>
+          <t>jay-ram.mishra@soprasteria.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1383,22 +1451,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-07-27 19:48:51.940000</t>
+          <t>2026-07-28 11:25:17.873000</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1406,15 +1474,27 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>669034</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>669034</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>669034</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990270</t>
+          <t>WTI-20260728-3990978</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1424,27 +1504,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IBM India Private Limited</t>
+          <t>Alstom Transport India Limited-CRD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DR. MANI MADHUKAR</t>
+          <t>GADDANAKERI RANJITA D</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-29 09:00:00</t>
+          <t>2026-07-29 07:30:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9560055140</t>
+          <t>8095092251</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>manimad9@in.ibm.com</t>
+          <t>ranjita.d-gaddanakeri@alstomgroup.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,12 +1534,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-27 22:24:55.587000</t>
+          <t>2026-07-28 13:41:08.050000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1469,7 +1549,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Coimbatore</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1477,60 +1557,72 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990624</t>
+          <t>WTI-20260728-3991280</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SANJIB KUMAR SINHA</t>
+          <t>SHRUTHI BADIGA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-29 10:30:00</t>
+          <t>2026-07-29 07:30:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9899986149</t>
+          <t>9916006051</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sanjibks@microsoft.com</t>
+          <t>sb01380@citi.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-07-28 08:19:21.650000</t>
+          <t>2026-07-28 16:24:17.170000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1540,23 +1632,39 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1380.00 ] PkgID:[287795]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990594</t>
+          <t>WTI-20260728-3991054</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1566,27 +1674,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Concentrix Daksh Services India Private Limited</t>
+          <t>Kyndryl Solutions Private Limited</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MADHUSUDAN SHARMA</t>
+          <t>SHANKAR VITTALA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-29 19:05:00</t>
+          <t>2026-07-29 07:30:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9899692733</t>
+          <t>9686570780</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>madhusudan.sharma@concentrix.com</t>
+          <t>shankar.vittala@kyndryl.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1596,12 +1704,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-07-28 05:48:51.793000</t>
+          <t>2026-07-28 14:36:30.630000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1611,57 +1719,65 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Airport Transfer Rate : 1500.00 ] PkgID:[288392]</t>
-        </is>
-      </c>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990591</t>
+          <t>WTI-20260728-3991235</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Megha Arora</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Google India Private Limited</t>
+          <t>Concentrix Daksh Services India Private Limited</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TESH SODHI</t>
+          <t>YOGENDRA JAIN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-29 19:45:00</t>
+          <t>2026-07-29 08:00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+61478306191</t>
+          <t>9811804462</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tesh@google.com</t>
+          <t>megha.arora1@concentrix.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1671,12 +1787,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-07-28 05:35:25.300000</t>
+          <t>2026-07-28 16:10:52.890000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1686,7 +1802,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1694,60 +1810,72 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990386</t>
+          <t>WTI-20260728-3991023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Vishnu Dutt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Vishnu C/o Pernod Ricard India Private Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SUNDAR SRINIVASAN</t>
+          <t>MEGHA AGGARWAL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-29 21:20:00</t>
+          <t>2026-07-29 08:00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9849298624</t>
+          <t>9911176486</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>sundars@microsoft.com</t>
+          <t>megha.aggarwal@pernod-ricard.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-07-28 00:38:03.917000</t>
+          <t>2026-07-28 14:16:08.393000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1757,7 +1885,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1765,15 +1893,27 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990381</t>
+          <t>WTI-20260728-3990819</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1783,27 +1923,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Google India Private Limited</t>
+          <t>Alstom Transport India Limited-CRD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROEE ENGELBERG &amp; OR AMI</t>
+          <t>VIGNESH  G</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-29 21:30:00</t>
+          <t>2026-07-29 08:30:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+972507964986</t>
+          <t>6380240181</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>roee@google.com</t>
+          <t>vignesh.g-1@alstomgroup.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1813,17 +1953,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-28 00:21:30.277000</t>
+          <t>2026-07-28 11:49:22.350000</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1833,7 +1973,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1851,61 +1991,57 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Airport - Transfer Rate : 2650.00 ] PkgID:[194158]</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990387</t>
+          <t>WTI-20260728-3990748</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Bhushan Shintre</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Citibank  NA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SUNDAR SRINIVASAN</t>
+          <t>SEAN SIM DIRECTOR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-30 08:00:00</t>
+          <t>2026-07-29 08:45:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9849298624</t>
+          <t>9923445651</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>sundars@microsoft.com</t>
+          <t>Sean.sim@citi.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-28 00:38:58.967000</t>
+          <t>2026-07-28 11:03:15.803000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1915,53 +2051,65 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+          <t>Outstation</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990095</t>
+          <t>WTI-20260728-3990929</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nishant Marathe</t>
+          <t>SHABINA ENGINEER</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BP Business Solutions India Private Ltd- SEZ</t>
+          <t>IBM India Private Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CHANDRA KUMAR MEDA + KULEN MARKANDU</t>
+          <t>GAURAV AGARWAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-30 08:30:00</t>
+          <t>2026-07-29 09:30:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+44758600150</t>
+          <t>8800336379</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>chandra.kumar@bp.com</t>
+          <t>SHABINA.ENGINEER@ibm.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1971,22 +2119,22 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-07-27 19:49:13.657000</t>
+          <t>2026-07-28 13:10:49.553000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Ahmedabad Hub1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1994,15 +2142,27 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990628</t>
+          <t>WTI-20260728-3990924</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2017,22 +2177,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANJIB KUMAR SINHA</t>
+          <t>ANUJH TEWARI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-30 09:00:00</t>
+          <t>2026-07-29 09:30:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9899986149</t>
+          <t>9755360101</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>sanjibks@microsoft.com</t>
+          <t>anujhtewari@microsoft.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2042,12 +2202,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-28 08:26:48.357000</t>
+          <t>2026-07-28 13:07:09.820000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2057,7 +2217,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2065,70 +2225,82 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990629</t>
+          <t>WTI-20260728-3991170</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Citigroup Global Markets India Pvt. Ltd. (CGM)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANJIB KUMAR SINHA</t>
+          <t>AMULYA GOYAL // DYLAN FERNANDES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-30 15:15:00</t>
+          <t>2026-07-29 10:40:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9899986149</t>
+          <t>9967045370</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>sanjibks@microsoft.com</t>
+          <t>amulya.goyal@citi.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Priya Rautela</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-28 08:28:01.800000</t>
+          <t>2026-07-28 15:41:01.347000</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2136,60 +2308,72 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990388</t>
+          <t>WTI-20260728-3990824</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Manimegalai R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>IBM India Private Limited</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SUNDAR SRINIVASAN</t>
+          <t>ABHAY SHARMA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-31 06:00:00</t>
+          <t>2026-07-29 10:55:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9849298624</t>
+          <t>9880601205</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>sundars@microsoft.com</t>
+          <t>Abhay.Sharma@in.ibm.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Nigam Sharma</t>
+          <t>Yudhveer Singh W04209</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-07-28 00:39:47.247000</t>
+          <t>2026-07-28 11:52:47.863000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2199,7 +2383,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2207,45 +2391,57 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTI-20260727-3990096</t>
+          <t>WTI-20260728-3991202</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nishant Marathe</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BP Business Solutions India Private Ltd- SEZ</t>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHANDRA KUMAR MEDA + KULEN MARKANDU</t>
+          <t>MAHESH DUBEY</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-31 08:30:00</t>
+          <t>2026-07-29 11:00:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+44758600150</t>
+          <t>8931038516</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>chandra.kumar@bp.com</t>
+          <t>md56125@citi.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2255,12 +2451,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ashish.Dagoria</t>
+          <t>Suhani Goenka</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-27 19:49:29.777000</t>
+          <t>2026-07-28 15:59:05.793000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2270,7 +2466,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2278,15 +2474,27 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WTI-20260728-3990643</t>
+          <t>WTI-20260728-3991085</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2301,22 +2509,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PRASANNA RAJAN</t>
+          <t>DIVYA DOGRA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-31 13:15:00</t>
+          <t>2026-07-29 13:40:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>8489249573</t>
+          <t>9818755114</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>prarajan@microsoft.com</t>
+          <t>divyadogra@microsoft.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2326,12 +2534,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Suhani Goenka</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-28 09:17:59.347000</t>
+          <t>2026-07-28 14:51:50.273000</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2341,20 +2549,945 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>6142096</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Airport - Transfer Rate : 1500.00 ] PkgID:[243637]</t>
+      <c r="Q26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3991239</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Megha Arora</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Concentrix Daksh Services India Private Limited</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>YOGENDRA JAIN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-07-29 16:20:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>9811804462</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>megha.arora1@concentrix.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Suhani Goenka</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:13:00.530000</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Airport Transfer Rate : 1500.00 ] PkgID:[288380]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990766</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SANJIB BISWAS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8008889329</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sanjib.Biswas@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:17:41.153000</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990981</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alstom Transport India Limited-CRD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GADDANAKERI RANJITA D</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:30:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8095092251</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ranjita.d-gaddanakeri@alstomgroup.com</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:42:20.687000</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1800.00 ] PkgID:[173425]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990769</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SANJIB BISWAS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8008889329</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sanjib.Biswas@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:19:14.533000</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990861</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>B SRI RAM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+14252833939</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>v-poojakadwa@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-28 12:25:23.597000</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990826</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Manimegalai R</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IBM India Private Limited</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ABHAY SHARMA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-07-30 08:00:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>9880601205</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Abhay.Sharma@in.ibm.com</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:53:29.067000</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3991183</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Citigroup Global Markets India Pvt. Ltd. (CGM)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AMULYA GOYAL // DYLAN FERNANDES</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-07-30 09:00:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>9967045370</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>amulya.goyal@citi.com</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Suhani Goenka</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-28 15:48:38.803000</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>AG79578</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990698</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>IBM India Private Limited</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RISHAV RAJ</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-07-30 10:00:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8800549154</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rishav.raj4@ibm.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-28 10:25:07.597000</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3991204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MAHESH DUBEY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-07-30 11:00:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8931038516</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>md56125@citi.com</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Suhani Goenka</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-28 15:59:25.420000</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3990775</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SANJIB BISWAS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-07-31 07:00:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8008889329</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sanjib.Biswas@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-28 11:19:48.370000</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WTI-20260728-3991286</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SHRUTHI BADIGA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>9916006051</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sb01380@citi.com</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Suhani Goenka</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:25:46.907000</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>sb01380</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1380.00 ] PkgID:[287795]</t>
         </is>
       </c>
     </row>
